--- a/gbo_price_full.xlsx
+++ b/gbo_price_full.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Новая папка\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Новая папка\Сайт\Архив\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72FCB39D-8740-40A7-886B-C465DA096B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52A3202B-FB08-4063-B4BA-996C76BCF20A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -700,14 +700,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="72.85546875" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -721,7 +721,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1603</v>
       </c>
@@ -732,13 +732,10 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>5200</v>
-      </c>
-      <c r="E2">
         <v>7500</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -749,13 +746,10 @@
         <v>4</v>
       </c>
       <c r="D3">
-        <v>4800</v>
-      </c>
-      <c r="E3">
         <v>7000</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1419</v>
       </c>
@@ -766,13 +760,10 @@
         <v>4</v>
       </c>
       <c r="D4">
-        <v>4900</v>
-      </c>
-      <c r="E4">
         <v>7000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -783,13 +774,10 @@
         <v>4</v>
       </c>
       <c r="D5">
-        <v>6700</v>
-      </c>
-      <c r="E5">
         <v>9000</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -800,13 +788,10 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>6500</v>
-      </c>
-      <c r="E6">
         <v>9000</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1853</v>
       </c>
@@ -817,13 +802,10 @@
         <v>4</v>
       </c>
       <c r="D7">
-        <v>7165</v>
-      </c>
-      <c r="E7">
         <v>9000</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -834,13 +816,10 @@
         <v>4</v>
       </c>
       <c r="D8">
-        <v>358</v>
-      </c>
-      <c r="E8">
         <v>700</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2562</v>
       </c>
@@ -851,13 +830,10 @@
         <v>4</v>
       </c>
       <c r="D9">
-        <v>410</v>
-      </c>
-      <c r="E9">
         <v>800</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -868,13 +844,10 @@
         <v>4</v>
       </c>
       <c r="D10">
-        <v>362</v>
-      </c>
-      <c r="E10">
         <v>800</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -885,13 +858,10 @@
         <v>4</v>
       </c>
       <c r="D11">
-        <v>415</v>
-      </c>
-      <c r="E11">
         <v>800</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,13 +872,10 @@
         <v>4</v>
       </c>
       <c r="D12">
-        <v>726</v>
-      </c>
-      <c r="E12">
         <v>1300</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
@@ -919,13 +886,10 @@
         <v>4</v>
       </c>
       <c r="D13">
-        <v>128</v>
-      </c>
-      <c r="E13">
         <v>450</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -936,13 +900,10 @@
         <v>4</v>
       </c>
       <c r="D14">
-        <v>387</v>
-      </c>
-      <c r="E14">
         <v>1300</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
@@ -953,13 +914,10 @@
         <v>4</v>
       </c>
       <c r="D15">
-        <v>214</v>
-      </c>
-      <c r="E15">
         <v>800</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>408</v>
       </c>
@@ -970,13 +928,10 @@
         <v>4</v>
       </c>
       <c r="D16">
-        <v>423</v>
-      </c>
-      <c r="E16">
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -987,13 +942,10 @@
         <v>4</v>
       </c>
       <c r="D17">
-        <v>365</v>
-      </c>
-      <c r="E17">
         <v>800</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>20</v>
       </c>
@@ -1004,13 +956,10 @@
         <v>4</v>
       </c>
       <c r="D18">
-        <v>110</v>
-      </c>
-      <c r="E18">
         <v>400</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
@@ -1021,13 +970,10 @@
         <v>4</v>
       </c>
       <c r="D19">
-        <v>65</v>
-      </c>
-      <c r="E19">
         <v>300</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
@@ -1038,13 +984,10 @@
         <v>4</v>
       </c>
       <c r="D20">
-        <v>423</v>
-      </c>
-      <c r="E20">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>21</v>
       </c>
@@ -1055,13 +998,10 @@
         <v>4</v>
       </c>
       <c r="D21">
-        <v>592</v>
-      </c>
-      <c r="E21">
         <v>900</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
@@ -1072,13 +1012,10 @@
         <v>4</v>
       </c>
       <c r="D22">
-        <v>16</v>
-      </c>
-      <c r="E22">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>25</v>
       </c>
@@ -1089,13 +1026,10 @@
         <v>4</v>
       </c>
       <c r="D23">
-        <v>24</v>
-      </c>
-      <c r="E23">
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>26</v>
       </c>
@@ -1106,13 +1040,10 @@
         <v>4</v>
       </c>
       <c r="D24">
-        <v>3580</v>
-      </c>
-      <c r="E24">
         <v>6000</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>27</v>
       </c>
@@ -1123,13 +1054,10 @@
         <v>4</v>
       </c>
       <c r="D25">
-        <v>4165</v>
-      </c>
-      <c r="E25">
         <v>8000</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
@@ -1140,13 +1068,10 @@
         <v>4</v>
       </c>
       <c r="D26">
-        <v>13500</v>
-      </c>
-      <c r="E26">
         <v>18000</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>30</v>
       </c>
@@ -1157,13 +1082,10 @@
         <v>4</v>
       </c>
       <c r="D27">
-        <v>1052</v>
-      </c>
-      <c r="E27">
         <v>1500</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>32</v>
       </c>
@@ -1174,13 +1096,10 @@
         <v>4</v>
       </c>
       <c r="D28">
-        <v>1066</v>
-      </c>
-      <c r="E28">
         <v>1500</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>34</v>
       </c>
@@ -1191,13 +1110,10 @@
         <v>4</v>
       </c>
       <c r="D29">
-        <v>268</v>
-      </c>
-      <c r="E29">
         <v>550</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>2192</v>
       </c>
@@ -1208,13 +1124,10 @@
         <v>4</v>
       </c>
       <c r="D30">
-        <v>384</v>
-      </c>
-      <c r="E30">
         <v>800</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>2191</v>
       </c>
@@ -1225,13 +1138,10 @@
         <v>4</v>
       </c>
       <c r="D31">
-        <v>373</v>
-      </c>
-      <c r="E31">
         <v>750</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>1192</v>
       </c>
@@ -1242,13 +1152,10 @@
         <v>4</v>
       </c>
       <c r="D32">
-        <v>890</v>
-      </c>
-      <c r="E32">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>35</v>
       </c>
@@ -1259,13 +1166,10 @@
         <v>4</v>
       </c>
       <c r="D33">
-        <v>3610</v>
-      </c>
-      <c r="E33">
         <v>5600</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>36</v>
       </c>
@@ -1276,13 +1180,10 @@
         <v>4</v>
       </c>
       <c r="D34">
-        <v>730</v>
-      </c>
-      <c r="E34">
         <v>1300</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>37</v>
       </c>
@@ -1293,13 +1194,10 @@
         <v>4</v>
       </c>
       <c r="D35">
-        <v>720</v>
-      </c>
-      <c r="E35">
         <v>1300</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>38</v>
       </c>
@@ -1310,13 +1208,10 @@
         <v>4</v>
       </c>
       <c r="D36">
-        <v>5950</v>
-      </c>
-      <c r="E36">
         <v>8000</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>39</v>
       </c>
@@ -1327,13 +1222,10 @@
         <v>4</v>
       </c>
       <c r="D37">
-        <v>1658</v>
-      </c>
-      <c r="E37">
         <v>3000</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>1392</v>
       </c>
@@ -1344,13 +1236,10 @@
         <v>4</v>
       </c>
       <c r="D38">
-        <v>4845</v>
-      </c>
-      <c r="E38">
         <v>7000</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>40</v>
       </c>
@@ -1361,13 +1250,10 @@
         <v>4</v>
       </c>
       <c r="D39">
-        <v>3600</v>
-      </c>
-      <c r="E39">
         <v>4500</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>2042</v>
       </c>
@@ -1378,13 +1264,10 @@
         <v>4</v>
       </c>
       <c r="D40">
-        <v>1356</v>
-      </c>
-      <c r="E40">
         <v>3000</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>41</v>
       </c>
@@ -1395,13 +1278,10 @@
         <v>4</v>
       </c>
       <c r="D41">
-        <v>1680</v>
-      </c>
-      <c r="E41">
         <v>3000</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>43</v>
       </c>
@@ -1412,13 +1292,10 @@
         <v>4</v>
       </c>
       <c r="D42">
-        <v>4610</v>
-      </c>
-      <c r="E42">
         <v>6000</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>45</v>
       </c>
@@ -1429,13 +1306,10 @@
         <v>4</v>
       </c>
       <c r="D43">
-        <v>1100</v>
-      </c>
-      <c r="E43">
         <v>1500</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>46</v>
       </c>
@@ -1446,13 +1320,10 @@
         <v>4</v>
       </c>
       <c r="D44">
-        <v>237</v>
-      </c>
-      <c r="E44">
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>47</v>
       </c>
@@ -1463,13 +1334,10 @@
         <v>4</v>
       </c>
       <c r="D45">
-        <v>58</v>
-      </c>
-      <c r="E45">
         <v>150</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>49</v>
       </c>
@@ -1480,13 +1348,10 @@
         <v>51</v>
       </c>
       <c r="D46">
-        <v>237</v>
-      </c>
-      <c r="E46">
         <v>450</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>52</v>
       </c>
@@ -1497,13 +1362,10 @@
         <v>51</v>
       </c>
       <c r="D47">
-        <v>35</v>
-      </c>
-      <c r="E47">
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>54</v>
       </c>
@@ -1514,13 +1376,10 @@
         <v>51</v>
       </c>
       <c r="D48">
-        <v>129</v>
-      </c>
-      <c r="E48">
         <v>250</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>55</v>
       </c>
@@ -1531,13 +1390,10 @@
         <v>4</v>
       </c>
       <c r="D49">
-        <v>120</v>
-      </c>
-      <c r="E49">
         <v>300</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>2203</v>
       </c>
@@ -1548,13 +1404,10 @@
         <v>4</v>
       </c>
       <c r="D50">
-        <v>73</v>
-      </c>
-      <c r="E50">
         <v>300</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>1932</v>
       </c>
@@ -1565,13 +1418,10 @@
         <v>4</v>
       </c>
       <c r="D51">
-        <v>275</v>
-      </c>
-      <c r="E51">
         <v>600</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>56</v>
       </c>
@@ -1582,13 +1432,10 @@
         <v>4</v>
       </c>
       <c r="D52">
-        <v>72</v>
-      </c>
-      <c r="E52">
         <v>250</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>57</v>
       </c>
@@ -1599,13 +1446,10 @@
         <v>4</v>
       </c>
       <c r="D53">
-        <v>52</v>
-      </c>
-      <c r="E53">
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>59</v>
       </c>
@@ -1616,13 +1460,10 @@
         <v>4</v>
       </c>
       <c r="D54">
-        <v>130</v>
-      </c>
-      <c r="E54">
         <v>250</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>61</v>
       </c>
@@ -1633,13 +1474,10 @@
         <v>4</v>
       </c>
       <c r="D55">
-        <v>229</v>
-      </c>
-      <c r="E55">
         <v>350</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>63</v>
       </c>
@@ -1650,13 +1488,10 @@
         <v>4</v>
       </c>
       <c r="D56">
-        <v>20</v>
-      </c>
-      <c r="E56">
         <v>50</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>65</v>
       </c>
@@ -1667,13 +1502,10 @@
         <v>4</v>
       </c>
       <c r="D57">
-        <v>81</v>
-      </c>
-      <c r="E57">
         <v>200</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>67</v>
       </c>
@@ -1684,13 +1516,10 @@
         <v>51</v>
       </c>
       <c r="D58">
-        <v>245</v>
-      </c>
-      <c r="E58">
         <v>400</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>69</v>
       </c>
@@ -1701,13 +1530,10 @@
         <v>51</v>
       </c>
       <c r="D59">
-        <v>68</v>
-      </c>
-      <c r="E59">
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>2615</v>
       </c>
@@ -1718,13 +1544,10 @@
         <v>51</v>
       </c>
       <c r="D60">
-        <v>118</v>
-      </c>
-      <c r="E60">
         <v>350</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>69</v>
       </c>
@@ -1735,13 +1558,10 @@
         <v>51</v>
       </c>
       <c r="D61">
-        <v>68</v>
-      </c>
-      <c r="E61">
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>70</v>
       </c>
@@ -1752,13 +1572,10 @@
         <v>51</v>
       </c>
       <c r="D62">
-        <v>182</v>
-      </c>
-      <c r="E62">
         <v>350</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>2615</v>
       </c>
@@ -1769,9 +1586,6 @@
         <v>51</v>
       </c>
       <c r="D63">
-        <v>118</v>
-      </c>
-      <c r="E63">
         <v>250</v>
       </c>
     </row>
